--- a/week09/output/크롤링_리포트.xlsx
+++ b/week09/output/크롤링_리포트.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>130건</t>
+          <t>461건</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3분 22초</t>
+          <t>3분 28초</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>130</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
